--- a/artfynd/A 24635-2025 artfynd.xlsx
+++ b/artfynd/A 24635-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,6 +1232,108 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125708069</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långmyrtjärnen, Långmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>519998</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6967847</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24635-2025 artfynd.xlsx
+++ b/artfynd/A 24635-2025 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>125708069</v>
       </c>
       <c r="B7" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24635-2025 artfynd.xlsx
+++ b/artfynd/A 24635-2025 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>125708069</v>
       </c>
       <c r="B7" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24635-2025 artfynd.xlsx
+++ b/artfynd/A 24635-2025 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>125708069</v>
       </c>
       <c r="B7" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24635-2025 artfynd.xlsx
+++ b/artfynd/A 24635-2025 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>125708069</v>
       </c>
       <c r="B7" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24635-2025 artfynd.xlsx
+++ b/artfynd/A 24635-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839390</v>
+        <v>121476235</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmyrberget, Jmt</t>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519992</v>
+        <v>519974</v>
       </c>
       <c r="R2" t="n">
-        <v>6967862</v>
+        <v>6967729</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121478601</v>
+        <v>121477474</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyrberget, Långmyrberget, Jmt</t>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519990</v>
+        <v>519997</v>
       </c>
       <c r="R3" t="n">
-        <v>6967852</v>
+        <v>6967748</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -861,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121476235</v>
+        <v>121479450</v>
       </c>
       <c r="B4" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519974</v>
+        <v>520036</v>
       </c>
       <c r="R4" t="n">
-        <v>6967729</v>
+        <v>6967788</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,12 +999,7 @@
         <v>121478200</v>
       </c>
       <c r="B5" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121477474</v>
+        <v>121478601</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,34 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+          <t>Långmyrberget, Långmyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519997</v>
+        <v>519990</v>
       </c>
       <c r="R6" t="n">
-        <v>6967748</v>
+        <v>6967852</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1197,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125708069</v>
+        <v>121479593</v>
       </c>
       <c r="B7" t="n">
-        <v>80080</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,17 +1241,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långmyrtjärnen, Långmyrtjärnen, Jmt</t>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519998</v>
+        <v>520021</v>
       </c>
       <c r="R7" t="n">
-        <v>6967847</v>
+        <v>6967787</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,17 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,15 +1305,829 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121479853</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>520028</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6967759</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125708069</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långmyrtjärnen, Långmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>519998</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6967847</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119839390</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>519992</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6967862</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>varav 1 hane, den andra såg jag inte . Båda trummade</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121478101</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Oxtjärnen, Oxtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>520030</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6967798</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125708219</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långmyrtjärnen, Långmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>520045</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6967756</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>119839393</v>
+      </c>
+      <c r="B13" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långmyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>520122</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6967821</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125708240</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långmyrtjärnen, Långmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>520042</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6967770</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125708287</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långmyrtjärnen, Långmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>520039</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6967764</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24635-2025 artfynd.xlsx
+++ b/artfynd/A 24635-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121476235</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121477474</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121479450</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478200</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478601</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121479593</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121479853</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125708069</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839390</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1740,6 +1790,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121478101</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125708219</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1934,6 +1994,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839393</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2031,6 +2096,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125708240</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2128,8 +2198,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125708287</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>